--- a/artfynd/A 15094-2024 artfynd.xlsx
+++ b/artfynd/A 15094-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,59 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121171352</v>
+        <v>121171515</v>
       </c>
       <c r="B2" t="n">
-        <v>98104</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547791</v>
+        <v>547686</v>
       </c>
       <c r="R2" t="n">
-        <v>6346143</v>
+        <v>6346051</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,17 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>I gallrad drygt 100 årig barrskog ralldominerad</t>
+          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,6 +761,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>På tallåga</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -788,6 +779,671 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>109631373</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>N Dalen, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>547846</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6346202</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Mörlunda</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Fredrik Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Fredrik Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>124500705</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58238</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Strängen, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>547594</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6346148</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Mörlunda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Calle Ljungberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Calle Ljungberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121171352</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gällingsbotrakten, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>547791</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6346143</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Mörlunda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>I gallrad drygt 100 årig barrskog ralldominerad</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121171467</v>
+      </c>
+      <c r="B6" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Strängen, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>547581</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6346150</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Mörlunda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121171616</v>
+      </c>
+      <c r="B7" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gällingsbotrakten, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>547863</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6346137</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Mörlunda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Moa Berglund</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121171619</v>
+      </c>
+      <c r="B8" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gällingsbotrakten, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>547864</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6346164</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Mörlunda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Moa Berglund</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
         <is>
           <t>Ecogain</t>
         </is>

--- a/artfynd/A 15094-2024 artfynd.xlsx
+++ b/artfynd/A 15094-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121171515</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109631373</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1021,6 +1036,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124500705</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121171352</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1246,6 +1271,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121171467</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1347,6 +1377,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121171616</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1448,8 +1483,22 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121171619</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>